--- a/product_surveys/017_two_wheeler_user_experience_survey--product_surveys.xlsx
+++ b/product_surveys/017_two_wheeler_user_experience_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'scooter'}</t>
+          <t>scooter</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Scooter'}</t>
+          <t>Scooter</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'motorcycle'}</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Motorcycle'}</t>
+          <t>Motorcycle</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'design'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Design'}</t>
+          <t>Design</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'performance'}</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Performance'}</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'price'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Price'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'old'}</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Old'}</t>
+          <t>Old</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'honda'}</t>
+          <t>honda</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Honda'}</t>
+          <t>Honda</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'yamaha'}</t>
+          <t>yamaha</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Yamaha'}</t>
+          <t>Yamaha</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'scooter'}</t>
+          <t>scooter</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Scooter'}</t>
+          <t>Scooter</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'motorcycle'}</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Motorcycle'}</t>
+          <t>Motorcycle</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
